--- a/data/trans_camb/IP04F-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Edad-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,64</t>
+          <t>-3,61; 5,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 5,05</t>
+          <t>-4,77; 5,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,9</t>
+          <t>-2,79; 4,15</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,02; 148,48</t>
+          <t>-46,95; 146,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,09; 127,95</t>
+          <t>-57,7; 121,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 93,21</t>
+          <t>-38,41; 93,06</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 5,0</t>
+          <t>-3,99; 5,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 3,09</t>
+          <t>-4,0; 3,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,95</t>
+          <t>-3,06; 2,8</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,49; 64,85</t>
+          <t>-31,28; 70,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,25; 60,19</t>
+          <t>-44,12; 60,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 40,61</t>
+          <t>-31,12; 39,72</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; -0,88</t>
+          <t>-11,58; -1,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 1,32</t>
+          <t>-9,17; 1,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -1,33</t>
+          <t>-8,65; -1,5</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,12; -2,4</t>
+          <t>-73,99; -12,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 15,94</t>
+          <t>-61,47; 19,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,09; -11,49</t>
+          <t>-60,92; -15,23</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 4,13</t>
+          <t>-7,48; 4,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,63</t>
+          <t>-6,27; 4,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 2,71</t>
+          <t>-5,28; 3,25</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 36,85</t>
+          <t>-46,94; 43,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,42; 55,22</t>
+          <t>-46,69; 52,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,14; 26,49</t>
+          <t>-37,98; 31,81</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,06</t>
+          <t>-4,06; 1,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,17</t>
+          <t>-3,59; 1,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,63</t>
+          <t>-3,11; 0,31</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 11,47</t>
+          <t>-34,4; 11,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 14,4</t>
+          <t>-35,94; 17,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 7,46</t>
+          <t>-29,22; 3,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Edad-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,4</t>
+          <t>-3,31; 6,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 5,15</t>
+          <t>-5,27; 4,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,15</t>
+          <t>-2,91; 3,52</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 146,85</t>
+          <t>-44,62; 185,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 121,98</t>
+          <t>-63,72; 128,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,41; 93,06</t>
+          <t>-37,77; 78,45</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,46</t>
+          <t>-3,69; 5,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,3</t>
+          <t>-4,54; 3,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,8</t>
+          <t>-3,11; 2,85</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 70,03</t>
+          <t>-31,01; 64,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 60,25</t>
+          <t>-47,79; 54,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 39,72</t>
+          <t>-29,7; 39,43</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,58; -1,2</t>
+          <t>-11,42; -1,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 1,41</t>
+          <t>-9,8; 0,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,65; -1,5</t>
+          <t>-8,78; -1,48</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,99; -12,12</t>
+          <t>-73,6; -10,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 19,13</t>
+          <t>-64,28; 8,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -15,23</t>
+          <t>-61,72; -12,13</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 4,31</t>
+          <t>-8,14; 4,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 4,7</t>
+          <t>-5,72; 5,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,25</t>
+          <t>-5,61; 2,68</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 43,66</t>
+          <t>-49,48; 40,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 52,77</t>
+          <t>-44,8; 60,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 31,81</t>
+          <t>-38,64; 27,16</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1,02</t>
+          <t>-4,24; 1,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,26</t>
+          <t>-3,61; 1,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,31</t>
+          <t>-3,1; 0,44</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 11,24</t>
+          <t>-35,13; 11,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,94; 17,2</t>
+          <t>-35,0; 14,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 3,48</t>
+          <t>-29,73; 5,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04F-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04F-Edad-trans_camb.xlsx
@@ -495,12 +495,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1,21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,32</t>
+          <t>-4,93; 5,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 4,58</t>
+          <t>-3,13; 5,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,52</t>
+          <t>-2,75; 3,9</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-2,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>21,16%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,31%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,62; 185,32</t>
+          <t>-61,09; 127,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,72; 128,43</t>
+          <t>-44,02; 148,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 78,45</t>
+          <t>-37,48; 93,21</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,57</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,31</t>
+          <t>-4,21; 3,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 3,06</t>
+          <t>-4,76; 5,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,85</t>
+          <t>-2,94; 2,95</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-5,64%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>5,63%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-5,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 64,58</t>
+          <t>-43,25; 60,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,79; 54,76</t>
+          <t>-37,49; 64,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 39,43</t>
+          <t>-29,13; 40,61</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>-6,13</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-3,9</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,42; -1,21</t>
+          <t>-9,3; 1,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 0,78</t>
+          <t>-11,67; -0,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,78; -1,48</t>
+          <t>-8,92; -1,33</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-33,1%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>-50,33%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-33,1%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,6; -10,81</t>
+          <t>-61,59; 15,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,28; 8,56</t>
+          <t>-73,12; -2,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,72; -12,13</t>
+          <t>-62,09; -11,49</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>-1,77</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 4,05</t>
+          <t>-6,18; 4,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 5,02</t>
+          <t>-8,42; 4,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 2,68</t>
+          <t>-5,26; 2,71</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-7,88%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-13,5%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-7,88%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,48; 40,75</t>
+          <t>-46,42; 55,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 60,99</t>
+          <t>-50,27; 36,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 27,16</t>
+          <t>-37,14; 26,49</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>-1,49</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,01</t>
+          <t>-3,65; 1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,13</t>
+          <t>-4,02; 1,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,44</t>
+          <t>-3,09; 0,63</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-12,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>-14,31%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-12,97%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 11,42</t>
+          <t>-35,43; 14,4</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,0; 14,91</t>
+          <t>-34,82; 11,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 5,29</t>
+          <t>-29,15; 7,46</t>
         </is>
       </c>
     </row>
